--- a/영상주소.xlsx
+++ b/영상주소.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chajh\Documents\Codex\2026-10-05\referenced-chatgpt-conversation-this-is-an\outputs\somang-ecm-lessons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64DC9C5-8F49-4E0D-9B83-B42206167974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C587BF-5730-4B2A-AA78-5F71A2EE1AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16335" yWindow="-135" windowWidth="16470" windowHeight="28350" xr2:uid="{DA5EE867-B5C9-4E52-9EBA-71D3E77A1F57}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="30960" windowHeight="12120" xr2:uid="{DA5EE867-B5C9-4E52-9EBA-71D3E77A1F57}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>년</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,6 +64,21 @@
   </si>
   <si>
     <t>https://wonspapa.synology.me/photo/mo/sharing/9slX5KkOw</t>
+  </si>
+  <si>
+    <t>https://wonspapa.synology.me/photo/mo/sharing/zA6YO3v8Z</t>
+  </si>
+  <si>
+    <t>https://wonspapa.synology.me/photo/mo/sharing/IPYKGYGcw</t>
+  </si>
+  <si>
+    <t>https://wonspapa.synology.me/photo/mo/sharing/JSNgn6hQn</t>
+  </si>
+  <si>
+    <t>https://wonspapa.synology.me/photo/mo/sharing/xLtYsXIIV</t>
+  </si>
+  <si>
+    <t>https://wonspapa.synology.me/photo/mo/sharing/w9ZWTdvA6</t>
   </si>
 </sst>
 </file>
@@ -447,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8768633B-7FB2-4931-A8F5-0D2BBAB2B4AB}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="63.19921875" customWidth="1"/>
@@ -523,6 +538,76 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
